--- a/saans-aqi-upload/AQI_daily_city_level_delhi_2025_delhi_2025.xlsx
+++ b/saans-aqi-upload/AQI_daily_city_level_delhi_2025_delhi_2025.xlsx
@@ -51,7 +51,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -67,6 +66,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -434,7 +501,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C2" t="n">
         <v>355</v>
@@ -442,15 +509,33 @@
       <c r="D2" t="n">
         <v>126</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>144</v>
+      </c>
+      <c r="F2" t="n">
+        <v>184</v>
+      </c>
+      <c r="G2" t="n">
+        <v>197</v>
+      </c>
+      <c r="H2" t="n">
+        <v>83</v>
+      </c>
+      <c r="I2" t="n">
+        <v>61</v>
+      </c>
+      <c r="J2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K2" t="n">
+        <v>130</v>
+      </c>
+      <c r="L2" t="n">
+        <v>303</v>
+      </c>
+      <c r="M2" t="n">
+        <v>304</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -465,15 +550,33 @@
       <c r="D3" t="n">
         <v>125</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>217</v>
+      </c>
+      <c r="F3" t="n">
+        <v>145</v>
+      </c>
+      <c r="G3" t="n">
+        <v>158</v>
+      </c>
+      <c r="H3" t="n">
+        <v>83</v>
+      </c>
+      <c r="I3" t="n">
+        <v>79</v>
+      </c>
+      <c r="J3" t="n">
+        <v>52</v>
+      </c>
+      <c r="K3" t="n">
+        <v>123</v>
+      </c>
+      <c r="L3" t="n">
+        <v>366</v>
+      </c>
+      <c r="M3" t="n">
+        <v>372</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -488,15 +591,33 @@
       <c r="D4" t="n">
         <v>156</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>217</v>
+      </c>
+      <c r="F4" t="n">
+        <v>180</v>
+      </c>
+      <c r="G4" t="n">
+        <v>143</v>
+      </c>
+      <c r="H4" t="n">
+        <v>72</v>
+      </c>
+      <c r="I4" t="n">
+        <v>79</v>
+      </c>
+      <c r="J4" t="n">
+        <v>57</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88</v>
+      </c>
+      <c r="L4" t="n">
+        <v>309</v>
+      </c>
+      <c r="M4" t="n">
+        <v>342</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -511,15 +632,33 @@
       <c r="D5" t="n">
         <v>148</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>219</v>
+      </c>
+      <c r="F5" t="n">
+        <v>232</v>
+      </c>
+      <c r="G5" t="n">
+        <v>187</v>
+      </c>
+      <c r="H5" t="n">
+        <v>78</v>
+      </c>
+      <c r="I5" t="n">
+        <v>116</v>
+      </c>
+      <c r="J5" t="n">
+        <v>58</v>
+      </c>
+      <c r="K5" t="n">
+        <v>138</v>
+      </c>
+      <c r="L5" t="n">
+        <v>291</v>
+      </c>
+      <c r="M5" t="n">
+        <v>304</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -534,15 +673,33 @@
       <c r="D6" t="n">
         <v>119</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>163</v>
+      </c>
+      <c r="F6" t="n">
+        <v>119</v>
+      </c>
+      <c r="G6" t="n">
+        <v>203</v>
+      </c>
+      <c r="H6" t="n">
+        <v>89</v>
+      </c>
+      <c r="I6" t="n">
+        <v>97</v>
+      </c>
+      <c r="J6" t="n">
+        <v>67</v>
+      </c>
+      <c r="K6" t="n">
+        <v>159</v>
+      </c>
+      <c r="L6" t="n">
+        <v>202</v>
+      </c>
+      <c r="M6" t="n">
+        <v>327</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -557,15 +714,33 @@
       <c r="D7" t="n">
         <v>124</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>209</v>
+      </c>
+      <c r="F7" t="n">
+        <v>141</v>
+      </c>
+      <c r="G7" t="n">
+        <v>161</v>
+      </c>
+      <c r="H7" t="n">
+        <v>75</v>
+      </c>
+      <c r="I7" t="n">
+        <v>91</v>
+      </c>
+      <c r="J7" t="n">
+        <v>73</v>
+      </c>
+      <c r="K7" t="n">
+        <v>105</v>
+      </c>
+      <c r="L7" t="n">
+        <v>311</v>
+      </c>
+      <c r="M7" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -580,15 +755,33 @@
       <c r="D8" t="n">
         <v>202</v>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>261</v>
+      </c>
+      <c r="F8" t="n">
+        <v>153</v>
+      </c>
+      <c r="G8" t="n">
+        <v>209</v>
+      </c>
+      <c r="H8" t="n">
+        <v>85</v>
+      </c>
+      <c r="I8" t="n">
+        <v>114</v>
+      </c>
+      <c r="J8" t="n">
+        <v>82</v>
+      </c>
+      <c r="K8" t="n">
+        <v>73</v>
+      </c>
+      <c r="L8" t="n">
+        <v>322</v>
+      </c>
+      <c r="M8" t="n">
+        <v>308</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -603,15 +796,33 @@
       <c r="D9" t="n">
         <v>158</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>243</v>
+      </c>
+      <c r="F9" t="n">
+        <v>169</v>
+      </c>
+      <c r="G9" t="n">
+        <v>198</v>
+      </c>
+      <c r="H9" t="n">
+        <v>98</v>
+      </c>
+      <c r="I9" t="n">
+        <v>116</v>
+      </c>
+      <c r="J9" t="n">
+        <v>82</v>
+      </c>
+      <c r="K9" t="n">
+        <v>81</v>
+      </c>
+      <c r="L9" t="n">
+        <v>361</v>
+      </c>
+      <c r="M9" t="n">
+        <v>314</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -626,15 +837,33 @@
       <c r="D10" t="n">
         <v>209</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>246</v>
+      </c>
+      <c r="F10" t="n">
+        <v>151</v>
+      </c>
+      <c r="G10" t="n">
+        <v>235</v>
+      </c>
+      <c r="H10" t="n">
+        <v>81</v>
+      </c>
+      <c r="I10" t="n">
+        <v>81</v>
+      </c>
+      <c r="J10" t="n">
+        <v>105</v>
+      </c>
+      <c r="K10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L10" t="n">
+        <v>370</v>
+      </c>
+      <c r="M10" t="n">
+        <v>282</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -649,15 +878,33 @@
       <c r="D11" t="n">
         <v>197</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>256</v>
+      </c>
+      <c r="F11" t="n">
+        <v>189</v>
+      </c>
+      <c r="G11" t="n">
+        <v>215</v>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>76</v>
+      </c>
+      <c r="J11" t="n">
+        <v>80</v>
+      </c>
+      <c r="K11" t="n">
+        <v>170</v>
+      </c>
+      <c r="L11" t="n">
+        <v>362</v>
+      </c>
+      <c r="M11" t="n">
+        <v>259</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -672,15 +919,33 @@
       <c r="D12" t="n">
         <v>262</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>164</v>
+      </c>
+      <c r="F12" t="n">
+        <v>158</v>
+      </c>
+      <c r="G12" t="n">
+        <v>245</v>
+      </c>
+      <c r="H12" t="n">
+        <v>79</v>
+      </c>
+      <c r="I12" t="n">
+        <v>106</v>
+      </c>
+      <c r="J12" t="n">
+        <v>94</v>
+      </c>
+      <c r="K12" t="n">
+        <v>199</v>
+      </c>
+      <c r="L12" t="n">
+        <v>428</v>
+      </c>
+      <c r="M12" t="n">
+        <v>307</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -695,15 +960,33 @@
       <c r="D13" t="n">
         <v>228</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>166</v>
+      </c>
+      <c r="F13" t="n">
+        <v>162</v>
+      </c>
+      <c r="G13" t="n">
+        <v>195</v>
+      </c>
+      <c r="H13" t="n">
+        <v>105</v>
+      </c>
+      <c r="I13" t="n">
+        <v>94</v>
+      </c>
+      <c r="J13" t="n">
+        <v>108</v>
+      </c>
+      <c r="K13" t="n">
+        <v>167</v>
+      </c>
+      <c r="L13" t="n">
+        <v>418</v>
+      </c>
+      <c r="M13" t="n">
+        <v>349</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -718,15 +1001,33 @@
       <c r="D14" t="n">
         <v>179</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>178</v>
+      </c>
+      <c r="F14" t="n">
+        <v>141</v>
+      </c>
+      <c r="G14" t="n">
+        <v>187</v>
+      </c>
+      <c r="H14" t="n">
+        <v>79</v>
+      </c>
+      <c r="I14" t="n">
+        <v>120</v>
+      </c>
+      <c r="J14" t="n">
+        <v>109</v>
+      </c>
+      <c r="K14" t="n">
+        <v>189</v>
+      </c>
+      <c r="L14" t="n">
+        <v>404</v>
+      </c>
+      <c r="M14" t="n">
+        <v>431</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -741,15 +1042,33 @@
       <c r="D15" t="n">
         <v>198</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>194</v>
+      </c>
+      <c r="F15" t="n">
+        <v>135</v>
+      </c>
+      <c r="G15" t="n">
+        <v>156</v>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>90</v>
+      </c>
+      <c r="J15" t="n">
+        <v>108</v>
+      </c>
+      <c r="K15" t="n">
+        <v>211</v>
+      </c>
+      <c r="L15" t="n">
+        <v>387</v>
+      </c>
+      <c r="M15" t="n">
+        <v>461</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -764,15 +1083,33 @@
       <c r="D16" t="n">
         <v>85</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>180</v>
+      </c>
+      <c r="F16" t="n">
+        <v>292</v>
+      </c>
+      <c r="G16" t="n">
+        <v>140</v>
+      </c>
+      <c r="H16" t="n">
+        <v>51</v>
+      </c>
+      <c r="I16" t="n">
+        <v>77</v>
+      </c>
+      <c r="J16" t="n">
+        <v>112</v>
+      </c>
+      <c r="K16" t="n">
+        <v>233</v>
+      </c>
+      <c r="L16" t="n">
+        <v>386</v>
+      </c>
+      <c r="M16" t="n">
+        <v>427</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -787,15 +1124,33 @@
       <c r="D17" t="n">
         <v>99</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>220</v>
+      </c>
+      <c r="F17" t="n">
+        <v>278</v>
+      </c>
+      <c r="G17" t="n">
+        <v>111</v>
+      </c>
+      <c r="H17" t="n">
+        <v>67</v>
+      </c>
+      <c r="I17" t="n">
+        <v>118</v>
+      </c>
+      <c r="J17" t="n">
+        <v>121</v>
+      </c>
+      <c r="K17" t="n">
+        <v>245</v>
+      </c>
+      <c r="L17" t="n">
+        <v>377</v>
+      </c>
+      <c r="M17" t="n">
+        <v>354</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -810,15 +1165,33 @@
       <c r="D18" t="n">
         <v>108</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>204</v>
+      </c>
+      <c r="F18" t="n">
+        <v>168</v>
+      </c>
+      <c r="G18" t="n">
+        <v>104</v>
+      </c>
+      <c r="H18" t="n">
+        <v>70</v>
+      </c>
+      <c r="I18" t="n">
+        <v>91</v>
+      </c>
+      <c r="J18" t="n">
+        <v>114</v>
+      </c>
+      <c r="K18" t="n">
+        <v>254</v>
+      </c>
+      <c r="L18" t="n">
+        <v>351</v>
+      </c>
+      <c r="M18" t="n">
+        <v>334</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -833,15 +1206,33 @@
       <c r="D19" t="n">
         <v>145</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>219</v>
+      </c>
+      <c r="F19" t="n">
+        <v>179</v>
+      </c>
+      <c r="G19" t="n">
+        <v>81</v>
+      </c>
+      <c r="H19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I19" t="n">
+        <v>76</v>
+      </c>
+      <c r="J19" t="n">
+        <v>107</v>
+      </c>
+      <c r="K19" t="n">
+        <v>268</v>
+      </c>
+      <c r="L19" t="n">
+        <v>374</v>
+      </c>
+      <c r="M19" t="n">
+        <v>373</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -856,15 +1247,33 @@
       <c r="D20" t="n">
         <v>160</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>165</v>
+      </c>
+      <c r="F20" t="n">
+        <v>201</v>
+      </c>
+      <c r="G20" t="n">
+        <v>89</v>
+      </c>
+      <c r="H20" t="n">
+        <v>54</v>
+      </c>
+      <c r="I20" t="n">
+        <v>89</v>
+      </c>
+      <c r="J20" t="n">
+        <v>143</v>
+      </c>
+      <c r="K20" t="n">
+        <v>296</v>
+      </c>
+      <c r="L20" t="n">
+        <v>392</v>
+      </c>
+      <c r="M20" t="n">
+        <v>374</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -879,15 +1288,33 @@
       <c r="D21" t="n">
         <v>156</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>140</v>
+      </c>
+      <c r="F21" t="n">
+        <v>204</v>
+      </c>
+      <c r="G21" t="n">
+        <v>75</v>
+      </c>
+      <c r="H21" t="n">
+        <v>75</v>
+      </c>
+      <c r="I21" t="n">
+        <v>79</v>
+      </c>
+      <c r="J21" t="n">
+        <v>131</v>
+      </c>
+      <c r="K21" t="n">
+        <v>345</v>
+      </c>
+      <c r="L21" t="n">
+        <v>391</v>
+      </c>
+      <c r="M21" t="n">
+        <v>398</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -902,15 +1329,33 @@
       <c r="D22" t="n">
         <v>144</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>205</v>
+      </c>
+      <c r="F22" t="n">
+        <v>213</v>
+      </c>
+      <c r="G22" t="n">
+        <v>85</v>
+      </c>
+      <c r="H22" t="n">
+        <v>93</v>
+      </c>
+      <c r="I22" t="n">
+        <v>79</v>
+      </c>
+      <c r="J22" t="n">
+        <v>127</v>
+      </c>
+      <c r="K22" t="n">
+        <v>351</v>
+      </c>
+      <c r="L22" t="n">
+        <v>364</v>
+      </c>
+      <c r="M22" t="n">
+        <v>377</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -925,15 +1370,33 @@
       <c r="D23" t="n">
         <v>161</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>227</v>
+      </c>
+      <c r="F23" t="n">
+        <v>119</v>
+      </c>
+      <c r="G23" t="n">
+        <v>92</v>
+      </c>
+      <c r="H23" t="n">
+        <v>88</v>
+      </c>
+      <c r="I23" t="n">
+        <v>102</v>
+      </c>
+      <c r="J23" t="n">
+        <v>135</v>
+      </c>
+      <c r="K23" t="n">
+        <v>353</v>
+      </c>
+      <c r="L23" t="n">
+        <v>370</v>
+      </c>
+      <c r="M23" t="n">
+        <v>373</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -948,15 +1411,33 @@
       <c r="D24" t="n">
         <v>194</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>224</v>
+      </c>
+      <c r="F24" t="n">
+        <v>129</v>
+      </c>
+      <c r="G24" t="n">
+        <v>112</v>
+      </c>
+      <c r="H24" t="n">
+        <v>67</v>
+      </c>
+      <c r="I24" t="n">
+        <v>97</v>
+      </c>
+      <c r="J24" t="n">
+        <v>126</v>
+      </c>
+      <c r="K24" t="n">
+        <v>305</v>
+      </c>
+      <c r="L24" t="n">
+        <v>391</v>
+      </c>
+      <c r="M24" t="n">
+        <v>412</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -971,15 +1452,33 @@
       <c r="D25" t="n">
         <v>206</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>227</v>
+      </c>
+      <c r="F25" t="n">
+        <v>141</v>
+      </c>
+      <c r="G25" t="n">
+        <v>95</v>
+      </c>
+      <c r="H25" t="n">
+        <v>91</v>
+      </c>
+      <c r="I25" t="n">
+        <v>63</v>
+      </c>
+      <c r="J25" t="n">
+        <v>120</v>
+      </c>
+      <c r="K25" t="n">
+        <v>275</v>
+      </c>
+      <c r="L25" t="n">
+        <v>382</v>
+      </c>
+      <c r="M25" t="n">
+        <v>271</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -994,15 +1493,33 @@
       <c r="D26" t="n">
         <v>234</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>258</v>
+      </c>
+      <c r="F26" t="n">
+        <v>105</v>
+      </c>
+      <c r="G26" t="n">
+        <v>132</v>
+      </c>
+      <c r="H26" t="n">
+        <v>136</v>
+      </c>
+      <c r="I26" t="n">
+        <v>62</v>
+      </c>
+      <c r="J26" t="n">
+        <v>120</v>
+      </c>
+      <c r="K26" t="n">
+        <v>292</v>
+      </c>
+      <c r="L26" t="n">
+        <v>353</v>
+      </c>
+      <c r="M26" t="n">
+        <v>234</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1017,15 +1534,33 @@
       <c r="D27" t="n">
         <v>231</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>247</v>
+      </c>
+      <c r="F27" t="n">
+        <v>105</v>
+      </c>
+      <c r="G27" t="n">
+        <v>95</v>
+      </c>
+      <c r="H27" t="n">
+        <v>84</v>
+      </c>
+      <c r="I27" t="n">
+        <v>55</v>
+      </c>
+      <c r="J27" t="n">
+        <v>120</v>
+      </c>
+      <c r="K27" t="n">
+        <v>309</v>
+      </c>
+      <c r="L27" t="n">
+        <v>327</v>
+      </c>
+      <c r="M27" t="n">
+        <v>332</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1040,15 +1575,33 @@
       <c r="D28" t="n">
         <v>259</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>246</v>
+      </c>
+      <c r="F28" t="n">
+        <v>133</v>
+      </c>
+      <c r="G28" t="n">
+        <v>76</v>
+      </c>
+      <c r="H28" t="n">
+        <v>85</v>
+      </c>
+      <c r="I28" t="n">
+        <v>71</v>
+      </c>
+      <c r="J28" t="n">
+        <v>169</v>
+      </c>
+      <c r="K28" t="n">
+        <v>301</v>
+      </c>
+      <c r="L28" t="n">
+        <v>377</v>
+      </c>
+      <c r="M28" t="n">
+        <v>385</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1063,15 +1616,33 @@
       <c r="D29" t="n">
         <v>205</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>266</v>
+      </c>
+      <c r="F29" t="n">
+        <v>151</v>
+      </c>
+      <c r="G29" t="n">
+        <v>97</v>
+      </c>
+      <c r="H29" t="n">
+        <v>86</v>
+      </c>
+      <c r="I29" t="n">
+        <v>120</v>
+      </c>
+      <c r="J29" t="n">
+        <v>139</v>
+      </c>
+      <c r="K29" t="n">
+        <v>294</v>
+      </c>
+      <c r="L29" t="n">
+        <v>369</v>
+      </c>
+      <c r="M29" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1084,15 +1655,33 @@
       <c r="D30" t="n">
         <v>153</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>209</v>
+      </c>
+      <c r="F30" t="n">
+        <v>171</v>
+      </c>
+      <c r="G30" t="n">
+        <v>83</v>
+      </c>
+      <c r="H30" t="n">
+        <v>72</v>
+      </c>
+      <c r="I30" t="n">
+        <v>98</v>
+      </c>
+      <c r="J30" t="n">
+        <v>120</v>
+      </c>
+      <c r="K30" t="n">
+        <v>279</v>
+      </c>
+      <c r="L30" t="n">
+        <v>305</v>
+      </c>
+      <c r="M30" t="n">
+        <v>401</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1105,15 +1694,33 @@
       <c r="D31" t="n">
         <v>138</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>198</v>
+      </c>
+      <c r="F31" t="n">
+        <v>167</v>
+      </c>
+      <c r="G31" t="n">
+        <v>65</v>
+      </c>
+      <c r="H31" t="n">
+        <v>66</v>
+      </c>
+      <c r="I31" t="n">
+        <v>72</v>
+      </c>
+      <c r="J31" t="n">
+        <v>117</v>
+      </c>
+      <c r="K31" t="n">
+        <v>373</v>
+      </c>
+      <c r="L31" t="n">
+        <v>279</v>
+      </c>
+      <c r="M31" t="n">
+        <v>388</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1127,21 +1734,27 @@
         <v>160</v>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>241</v>
+      </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>59</v>
+      </c>
+      <c r="I32" t="n">
+        <v>79</v>
+      </c>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>218</v>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>373</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -1161,18 +1774,42 @@
           <t>Good</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1180,20 +1817,42 @@
           <t>Satisfactory</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
       <c r="D35" t="n">
         <v>2</v>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>11</v>
+      </c>
+      <c r="H35" t="n">
+        <v>29</v>
+      </c>
+      <c r="I35" t="n">
+        <v>23</v>
+      </c>
+      <c r="J35" t="n">
+        <v>10</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1210,15 +1869,33 @@
       <c r="D36" t="n">
         <v>20</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" t="n">
+        <v>24</v>
+      </c>
+      <c r="G36" t="n">
+        <v>14</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>20</v>
+      </c>
+      <c r="K36" t="n">
+        <v>9</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1235,15 +1912,33 @@
       <c r="D37" t="n">
         <v>9</v>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>20</v>
+      </c>
+      <c r="F37" t="n">
+        <v>7</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>11</v>
+      </c>
+      <c r="L37" t="n">
+        <v>3</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1257,16 +1952,36 @@
       <c r="C38" t="n">
         <v>2</v>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>7</v>
+      </c>
+      <c r="L38" t="n">
+        <v>24</v>
+      </c>
+      <c r="M38" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1274,18 +1989,42 @@
           <t>Severe</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3</v>
+      </c>
+      <c r="M39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -1339,14 +2078,30 @@
       <c r="E42" t="n">
         <v>100</v>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>100</v>
+      </c>
+      <c r="G42" t="n">
+        <v>100</v>
+      </c>
+      <c r="H42" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" t="n">
+        <v>100</v>
+      </c>
+      <c r="J42" t="n">
+        <v>100</v>
+      </c>
+      <c r="K42" t="n">
+        <v>100</v>
+      </c>
+      <c r="L42" t="n">
+        <v>100</v>
+      </c>
+      <c r="M42" t="n">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1435,28 +2190,64 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CO,NO2,OZONE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>PM2.5, O3, PM10</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PM10, CO</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>NO2, PM10, CO</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1464,28 +2255,64 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5, PM10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PM2.5, NO2, CO</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1493,28 +2320,64 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5, O3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NO2, CO, PM10</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>O3, PM2.5</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1522,28 +2385,64 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PM10, O3, PM2.5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CO, NO2, O3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1551,28 +2450,64 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CO,NO2,OZONE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>PM2.5, NO2, PM10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10, O3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CO, PM10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>CO, PM10</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>O3, PM2.5</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>O3, PM2.5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1580,28 +2515,64 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CO,NO2,OZONE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>O3, PM2.5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1609,28 +2580,64 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>CO, O3</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1638,28 +2645,64 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
+          <t>PM2.5, O3, PM10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>PM10, O3, PM2.5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>O3, PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>O3, CO</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,28 +2710,64 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10, O3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PM10, CO, O3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5, O3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,28 +2775,64 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NO2,PM10,PM2.5</t>
+          <t>PM10, PM2.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>O3, PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NO2, CO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PM10, SO2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1725,28 +2840,64 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
+          <t>PM10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1754,28 +2905,64 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NO2,PM10,PM2.5</t>
+          <t>PM10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PM2.5, CO, O3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1783,28 +2970,64 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
+          <t>PM10, O3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CO,OZONE,PM10</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PM10, NO2, O3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10, CO</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1812,28 +3035,64 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CO,NO2,OZONE</t>
+          <t>PM10, O3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+          <t>PM2.5, O3</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CO, PM10</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10, CO</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1841,28 +3100,64 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
+          <t>O3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CO,NO2,OZONE</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>PM10, CO</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1870,28 +3165,64 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM10</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+          <t>O3, PM2.5</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PM10, O3, PM2.5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1899,28 +3230,64 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
+          <t>PM2.5, O3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>O3, PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1928,28 +3295,64 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5, PM10</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CO,OZONE,PM10</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+          <t>O3, PM2.5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CO, PM10</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1957,28 +3360,64 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
+          <t>PM10, O3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CO,NO2,OZONE</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+          <t>O3, PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NO2, PM10, CO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1986,28 +3425,64 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
+          <t>PM2.5, PM10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CO, PM10</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CO, PM10</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2015,28 +3490,64 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CO,NO2,OZONE</t>
+          <t>O3, PM2.5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>PM2.5, CO, PM10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2044,28 +3555,64 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CO,NO2,OZONE</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>CO, PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2073,28 +3620,64 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5, O3</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2102,28 +3685,64 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
+          <t>O3, PM2.5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PM10, O3</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>PM2.5, NO2, CO</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2131,28 +3750,64 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
+          <t>O3, PM2.5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
+          <t>PM2.5, O3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>NO2, PM2.5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2160,28 +3815,64 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
+          <t>PM10</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>NO2, PM2.5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>CO, PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10, O3</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2189,28 +3880,64 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM10, PM2.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PM2.5, O3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2218,28 +3945,64 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OZONE,PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CO,NO2,PM10</t>
+          <t>PM10, PM2.5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NO2,OZONE,PM10</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CO, PM10</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O3, PM2.5</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2247,24 +4010,60 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM2.5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CO,NO2,OZONE</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5, CO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2272,24 +4071,60 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM10, PM2.5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CO,NO2,OZONE</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>PM10, PM2.5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>PM2.5, PM10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2297,31 +4132,47 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PM10,PM2.5</t>
+          <t>PM10, PM2.5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CO,NO2,OZONE</t>
+          <t>PM10, PM2.5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>O3, PM10, PM2.5</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>O3, PM10</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>PM10</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
